--- a/examples/medibec/deliverables/MediBec_CyberRiskGuardian_Workbook.xlsx
+++ b/examples/medibec/deliverables/MediBec_CyberRiskGuardian_Workbook.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId3"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author>Unknown Author</author>
   </authors>
@@ -46,6 +46,27 @@
           <t xml:space="preserve">Phishing is constant and attempts are increasing; lures already observed. Evidence: E4, E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>24</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C5" authorId="0">
       <text>
@@ -58,6 +79,27 @@
           <t xml:space="preserve">Healthcare is a sustained ransomware target; attempts rising. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>6</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C6" authorId="0">
       <text>
@@ -70,6 +112,27 @@
           <t xml:space="preserve">Conditional on an intrusion reaching administrative level (S1/S2). Evidence: E4, E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C7" authorId="0">
       <text>
@@ -82,6 +145,27 @@
           <t xml:space="preserve">Cloud storage is continuously scanned. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>25</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C8" authorId="0">
       <text>
@@ -94,6 +178,27 @@
           <t xml:space="preserve">Insider snooping is recurrent in healthcare; service-account anomaly observed. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>23</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C9" authorId="0">
       <text>
@@ -106,6 +211,27 @@
           <t xml:space="preserve">Edge-device exploitation campaigns are frequent. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C10" authorId="0">
       <text>
@@ -118,6 +244,27 @@
           <t xml:space="preserve">Targeting of devices is less frequent than IT, but collateral infection is common. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>20</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C11" authorId="0">
       <text>
@@ -130,6 +277,27 @@
           <t xml:space="preserve">Attempts ongoing; some will pass perimeter controls. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C12" authorId="0">
       <text>
@@ -142,6 +310,27 @@
           <t xml:space="preserve">Supply-chain attacks on healthcare vendors are recurrent. Evidence: E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C13" authorId="0">
       <text>
@@ -154,6 +343,27 @@
           <t xml:space="preserve">Integrity attacks are rarer than theft or encryption. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D4" authorId="0">
       <text>
@@ -166,6 +376,27 @@
           <t xml:space="preserve">Push MFA is bypassable by fatigue; no conditional access or macro blocking evidenced. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D5" authorId="0">
       <text>
@@ -178,6 +409,27 @@
           <t xml:space="preserve">Multiple weak links (triage, segmentation, backup isolation) but perimeter controls exist. Evidence: E2, E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>6</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D6" authorId="0">
       <text>
@@ -190,6 +442,27 @@
           <t xml:space="preserve">Isolation unknown; failures in E6 suggest exposure. Evidence: E2, E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D7" authorId="0">
       <text>
@@ -202,6 +475,27 @@
           <t xml:space="preserve">Depends on sharing configuration - unknown; E6 suggests weakness. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D8" authorId="0">
       <text>
@@ -214,6 +508,27 @@
           <t xml:space="preserve">Legitimate access bypasses perimeter controls; no analytics. Evidence: E6, E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D9" authorId="0">
       <text>
@@ -226,6 +541,27 @@
           <t xml:space="preserve">Patching lag documented; inventory incomplete. Evidence: E3, E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D10" authorId="0">
       <text>
@@ -238,6 +574,27 @@
           <t xml:space="preserve">Patch and segmentation constraints documented. Evidence: E3, E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>20</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D11" authorId="0">
       <text>
@@ -250,6 +607,27 @@
           <t xml:space="preserve">Evidence of mis-triaged alerts and uncorrelated signals. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D12" authorId="0">
       <text>
@@ -262,6 +640,27 @@
           <t xml:space="preserve">Controls over vendor access not evidenced. Evidence: E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D13" authorId="0">
       <text>
@@ -274,6 +673,27 @@
           <t xml:space="preserve">Requires write access; monitoring absent. Evidence: E8</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E4" authorId="0">
       <text>
@@ -286,6 +706,27 @@
           <t xml:space="preserve">Access to a subset of records; containment possible if detected. Evidence: E1, E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E5" authorId="0">
       <text>
@@ -298,6 +739,27 @@
           <t xml:space="preserve">Multi-day disruption of several clinics. Evidence: E1, E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>6</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E6" authorId="0">
       <text>
@@ -310,6 +772,27 @@
           <t xml:space="preserve">Partial loss of recent restore points. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E7" authorId="0">
       <text>
@@ -322,6 +805,27 @@
           <t xml:space="preserve">Partial data set exposed. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>25</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E8" authorId="0">
       <text>
@@ -334,6 +838,27 @@
           <t xml:space="preserve">Limited set of records. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E9" authorId="0">
       <text>
@@ -346,6 +871,27 @@
           <t xml:space="preserve">Foothold with some data access. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E10" authorId="0">
       <text>
@@ -358,6 +904,27 @@
           <t xml:space="preserve">Some devices unavailable at one clinic. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E11" authorId="0">
       <text>
@@ -370,6 +937,27 @@
           <t xml:space="preserve">Incident escalates before containment. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E12" authorId="0">
       <text>
@@ -382,6 +970,27 @@
           <t xml:space="preserve">Breach through one vendor path. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E13" authorId="0">
       <text>
@@ -394,6 +1003,27 @@
           <t xml:space="preserve">Limited record set altered and detected. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F4" authorId="0">
       <text>
@@ -406,6 +1036,27 @@
           <t xml:space="preserve">Full EHR access or pivot to ransomware. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F5" authorId="0">
       <text>
@@ -418,6 +1069,27 @@
           <t xml:space="preserve">Network-wide outage with data theft and failed recovery. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>6</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F6" authorId="0">
       <text>
@@ -430,6 +1102,27 @@
           <t xml:space="preserve">No usable backup for EHR. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F7" authorId="0">
       <text>
@@ -442,6 +1135,27 @@
           <t xml:space="preserve">Entire export history exposed. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>25</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F8" authorId="0">
       <text>
@@ -454,6 +1168,27 @@
           <t xml:space="preserve">Bulk extraction through the service account. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F9" authorId="0">
       <text>
@@ -466,6 +1201,27 @@
           <t xml:space="preserve">Precursor to network-wide ransomware. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F10" authorId="0">
       <text>
@@ -478,6 +1234,27 @@
           <t xml:space="preserve">Patient harm from altered or unavailable equipment. Evidence: E5</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F11" authorId="0">
       <text>
@@ -490,6 +1267,27 @@
           <t xml:space="preserve">Full ransomware and breach scenario. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F12" authorId="0">
       <text>
@@ -502,6 +1300,27 @@
           <t xml:space="preserve">EHR vendor compromise affecting all clinics. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F13" authorId="0">
       <text>
@@ -514,6 +1333,27 @@
           <t xml:space="preserve">Patient harm from undetected alteration. Evidence: E5</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G4" authorId="0">
       <text>
@@ -526,6 +1366,27 @@
           <t xml:space="preserve">Two-person team; alert triage weak; IR untested. Evidence: E3, E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G5" authorId="0">
       <text>
@@ -538,6 +1399,27 @@
           <t xml:space="preserve">Recovery and workarounds untested; small team. Evidence: E3, E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>6</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G6" authorId="0">
       <text>
@@ -550,6 +1432,27 @@
           <t xml:space="preserve">No restore testing evidence. Evidence: E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G7" authorId="0">
       <text>
@@ -562,6 +1465,27 @@
           <t xml:space="preserve">Logging and detection uncertain. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>25</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G8" authorId="0">
       <text>
@@ -574,6 +1498,27 @@
           <t xml:space="preserve">Logs exist but not monitored. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G9" authorId="0">
       <text>
@@ -586,6 +1531,27 @@
           <t xml:space="preserve">Detection of implants uncertain. Evidence: E3</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G10" authorId="0">
       <text>
@@ -598,6 +1564,27 @@
           <t xml:space="preserve">No device monitoring or inventory evidence. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G11" authorId="0">
       <text>
@@ -610,6 +1597,27 @@
           <t xml:space="preserve">Detection and response are the weak capability itself. Evidence: E3</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G12" authorId="0">
       <text>
@@ -622,6 +1630,27 @@
           <t xml:space="preserve">Limited visibility into vendor activity. Evidence: E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G13" authorId="0">
       <text>
@@ -634,6 +1663,27 @@
           <t xml:space="preserve">Backups exist but integrity verification absent. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H4" authorId="0">
       <text>
@@ -646,6 +1696,27 @@
           <t xml:space="preserve">Identity is the gateway to every crown jewel. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H5" authorId="0">
       <text>
@@ -658,6 +1729,27 @@
           <t xml:space="preserve">EHR and scheduling underpin care delivery. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>6</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H6" authorId="0">
       <text>
@@ -670,6 +1762,27 @@
           <t xml:space="preserve">Recoverability of every crown jewel depends on it. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H7" authorId="0">
       <text>
@@ -682,6 +1795,27 @@
           <t xml:space="preserve">Important but not essential to same-day care. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>25</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H8" authorId="0">
       <text>
@@ -694,6 +1828,27 @@
           <t xml:space="preserve">EHR confidentiality is core to trust. Evidence: E5</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H9" authorId="0">
       <text>
@@ -706,6 +1861,27 @@
           <t xml:space="preserve">Remote access and perimeter serve all clinics. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H10" authorId="0">
       <text>
@@ -718,6 +1894,27 @@
           <t xml:space="preserve">Direct link to patient safety. Evidence: E5</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H11" authorId="0">
       <text>
@@ -730,6 +1927,27 @@
           <t xml:space="preserve">Response capacity protects every service. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H12" authorId="0">
       <text>
@@ -742,6 +1960,27 @@
           <t xml:space="preserve">Vendors support crown-jewel systems. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H13" authorId="0">
       <text>
@@ -754,6 +1993,27 @@
           <t xml:space="preserve">Clinical record integrity underpins safe care. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J4" authorId="0">
       <text>
@@ -766,6 +2026,27 @@
           <t xml:space="preserve">Representative weakness: remote-access authentication accepting MFA push approval (CWE-308-type single-channel weakness). AV:N internet-reachable gateway; AC:L no special conditions; AT:N; PR:N attacker starts unauthenticated; UI:A user must actively approve; VC/VI:H full session on gateway; VA:N; SC:H EHR data behind the gateway; SI:L/SA:L limited downstream change/disruption. Applicability: moderate - human factor dominates.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>13</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J5" authorId="0">
       <text>
@@ -775,9 +2056,30 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Representative weakness: malicious macro document leading to code execution (initial vector in E6). AV:N delivered by e-mail; AC:L; AT:N; PR:N; UI:P user opens the document; VC/VI/VA:H on the workstation; SC/SI/SA:H because EHR and clinic systems are subsequently affected. CVSS describes the entry weakness only, not the enterprise impact.</t>
+          <t xml:space="preserve">Representative weakness: malicious macro document leading to code execution (initial vector in E6). AV:L - the document is delivered by e-mail but opened locally on the workstation (FIRST CVSS v4.0 user guide: document-based weaknesses are Local whatever the delivery channel); AC:L; AT:N; PR:N; UI:P user opens the document; VC/VI/VA:H on the workstation; SC/SI/SA:H because EHR and clinic systems are subsequently affected. CVSS describes the entry weakness only, not the enterprise impact.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>6</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>17</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J6" authorId="0">
       <text>
@@ -790,6 +2092,27 @@
           <t xml:space="preserve">Representative weakness: backup management console reachable from production network and trusting production administrator accounts. PR:H attacker already holds admin credentials; VC/VI/VA:H on the backup system; SA:H because recovery of all subsequent systems is lost.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J7" authorId="0">
       <text>
@@ -802,6 +2125,27 @@
           <t xml:space="preserve">Representative weakness: storage object accessible without authentication (CWE-284 misconfiguration). AV:N, AC:L, AT:N, PR:N, UI:N; confidentiality only (VC:H).</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J8" authorId="0">
       <text>
@@ -814,6 +2158,27 @@
           <t xml:space="preserve">Limited applicability: insider misuse is not a software vulnerability. Representative weakness used for the workbook: excessive privileges on an authenticated account (CWE-269). PR:L legitimate low-privilege access; VC:H bulk read; VI:L. Interpret with caution.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>12</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J9" authorId="0">
       <text>
@@ -826,6 +2191,27 @@
           <t xml:space="preserve">Representative weakness: unauthenticated remote code execution in an internet-facing gateway (typical of known-exploited edge vulnerabilities). All impacts High because the gateway fronts the internal network. Replace with the actual CVE vector once scan data is available.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>11</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J10" authorId="0">
       <text>
@@ -838,6 +2224,27 @@
           <t xml:space="preserve">Representative weakness: unpatched embedded service or default credential on a networked device. AV:A reachable from the clinic LAN/Wi-Fi only; PR:N; full device impact; SC/SI/SA:L onward effects. CVSS supplemental metric Safety (S:P) would apply but is not part of the base score.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J11" authorId="0">
       <text>
@@ -847,9 +2254,30 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Limited applicability: a detection gap is a control weakness, not a vulnerability. Representative weakness for the workbook: the undetected initial code-execution vector (macro/PowerShell, E6). Do not interpret the score as the severity of the detection gap.</t>
+          <t xml:space="preserve">Limited applicability: a detection gap is a control weakness, not a vulnerability. Representative weakness for the workbook: the undetected initial code-execution vector (macro/PowerShell, E6); AV:L because the malicious document is opened locally. Do not interpret the score as the severity of the detection gap.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>12</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J12" authorId="0">
       <text>
@@ -862,6 +2290,27 @@
           <t xml:space="preserve">Limited applicability: supplier concentration is not a single vulnerability. Representative weakness: standing authenticated remote-access channel. AT:P the vendor must first be compromised; PR:L vendor account; full impacts. Validate against actual vendor access design.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J13" authorId="0">
       <text>
@@ -874,6 +2323,27 @@
           <t xml:space="preserve">Representative weakness: authenticated user able to modify records beyond need (improper authorization, CWE-285). PR:L; VI:H; SI:H because pharmacy/lab downstream systems consume the altered data.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
@@ -891,7 +2361,7 @@
     <t xml:space="preserve">Source: MediBec Business Case v2.0b (fictional teaching case, M.-A. Leger) and CyberRiskGuardian Excel Guide v1.0c formulas.</t>
   </si>
   <si>
-    <t xml:space="preserve">All parameter values, CVSS vectors, costs and reductions are ANALYST ESTIMATES - VALIDATION REQUIRED. Scores are relative decision-support indicators, not loss predictions.</t>
+    <t xml:space="preserve">All parameter values, CVSS vectors, costs and reductions are ANALYTICAL ESTIMATES — VALIDATION REQUIRED. Scores are relative decision-support indicators, not loss predictions.</t>
   </si>
   <si>
     <t xml:space="preserve">Colour legend:  blue text = input you may edit  |  black = formula  |  green = link to another sheet  |  yellow fill = key assumption.</t>
@@ -936,13 +2406,13 @@
     <t xml:space="preserve">  Ratio = Residual / Tolerated ;  Cost-effectiveness = (Estimated - Residual) / Cost x 1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Note: the template computes Residual as ABS(L - R). Because both reductions are kept within 0-1, L - R is always &gt;= 0 and the two are identical; a validity check column is included.</t>
+    <t xml:space="preserve">Note: Residual = Estimated - Mitigated; the corrected template guards it with MAX(0, L - R) (never ABS). Both reductions are kept within 0-1, so L - R is always &gt;= 0; a validity check column is included.</t>
   </si>
   <si>
     <t xml:space="preserve">How to use: change blue cells on Parameters / Inputs / Portfolio, then recalculate (Formulas &gt; Calculate Now if manual).</t>
   </si>
   <si>
-    <t xml:space="preserve">Analyse - CyberRiskGuardian KRIs (Excel Guide v1.0c formulas)</t>
+    <t xml:space="preserve">Analyse - CyberRiskGuardian risk indices (Excel Guide v1.0c formulas; not KRIs)</t>
   </si>
   <si>
     <t xml:space="preserve">Green = linked from Inputs / Portfolio / Parameters; black = formula.</t>
@@ -1038,7 +2508,7 @@
     <t xml:space="preserve">Risk appetite (analyst estimate)</t>
   </si>
   <si>
-    <t xml:space="preserve">Analyst estimate - validation required. Case states 0.40 normalized tolerance; see report s.4.</t>
+    <t xml:space="preserve">Analytical estimate — validation required. Case states 0.40 normalized tolerance; see report s.4.</t>
   </si>
   <si>
     <t xml:space="preserve">Multiplication factor</t>
@@ -1077,7 +2547,7 @@
     <t xml:space="preserve">Case escalation - Board acceptance threshold</t>
   </si>
   <si>
-    <t xml:space="preserve">Scenario inputs (0-1 scale unless stated) - Analyst estimates, validation required</t>
+    <t xml:space="preserve">Scenario inputs (0-1 scale unless stated) - Analytical estimates — validation required</t>
   </si>
   <si>
     <t xml:space="preserve">CVSS v4.0 vector</t>
@@ -1125,7 +2595,7 @@
     <t xml:space="preserve">Ransomware disrupting EHR access and clinic operations across the network</t>
   </si>
   <si>
-    <t xml:space="preserve">CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:P/VC:H/VI:H/VA:H/SC:H/SI:H/SA:H</t>
+    <t xml:space="preserve">CVSS:4.0/AV:L/AC:L/AT:N/PR:N/UI:P/VC:H/VI:H/VA:H/SC:H/SI:H/SA:H</t>
   </si>
   <si>
     <t xml:space="preserve">S3</t>
@@ -1179,7 +2649,7 @@
     <t xml:space="preserve">Detection and response gaps allow an intrusion to persist and escalate</t>
   </si>
   <si>
-    <t xml:space="preserve">CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:P/VC:H/VI:H/VA:L/SC:H/SI:L/SA:L</t>
+    <t xml:space="preserve">CVSS:4.0/AV:L/AC:L/AT:N/PR:N/UI:P/VC:H/VI:H/VA:L/SC:H/SI:L/SA:L</t>
   </si>
   <si>
     <t xml:space="preserve">S9</t>
@@ -1464,7 +2934,7 @@
     <t xml:space="preserve">Allocation assumption: each initiative's Year-1 cost is split equally across the scenarios it addresses, so shared controls are never charged in full to several scenarios.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cyber-insurance premium is excluded (Evidence gap - broker quotation required).</t>
+    <t xml:space="preserve">Cyber-insurance premium is excluded (Information gap - broker quotation required).</t>
   </si>
   <si>
     <t xml:space="preserve">Sensitivity - lower / central / higher cases</t>
@@ -1590,7 +3060,7 @@
     <t xml:space="preserve">Cybercriminal (initial-access broker or ransomware affiliate).</t>
   </si>
   <si>
-    <t xml:space="preserve">Push-based MFA without number matching or phishing resistance (E6 - validate); No evidence of conditional access (geo/device) policies; Internet-sourced macro documents reach users (E6); Awareness programme maturity unknown (Evidence gap)</t>
+    <t xml:space="preserve">Push-based MFA without number matching or phishing resistance (E6 - validate); No evidence of conditional access (geo/device) policies; Internet-sourced macro documents reach users (E6); Awareness programme maturity unknown (Information gap)</t>
   </si>
   <si>
     <t xml:space="preserve">Email filtering / antimalware (E2 - effectiveness unknown); MFA push on remote access (E6); EDR alerting (E6 - triage weak)</t>
@@ -1620,7 +3090,7 @@
     <t xml:space="preserve">Ransomware-as-a-service affiliate (double extortion).</t>
   </si>
   <si>
-    <t xml:space="preserve">Macro execution and weak alert triage (E6); Segmentation between clinics, servers and backups not evidenced (E2, E7); Privileged credential hygiene unknown (Evidence gap); Clinic downtime procedures untested (E7)</t>
+    <t xml:space="preserve">Macro execution and weak alert triage (E6); Segmentation between clinics, servers and backups not evidenced (E2, E7); Privileged credential hygiene unknown (Information gap); Clinic downtime procedures untested (E7)</t>
   </si>
   <si>
     <t xml:space="preserve">Firewalls, IDS/IPS, antimalware (E2); EDR (E6); On-site and off-site backups (E2 - isolation and testing unknown); Incident command structure defined (E6 - untested)</t>
@@ -1638,7 +3108,7 @@
     <t xml:space="preserve">0-24 months</t>
   </si>
   <si>
-    <t xml:space="preserve">Representative weakness: malicious macro document leading to code execution (initial vector in E6). AV:N delivered by e-mail; AC:L; AT:N; PR:N; UI:P user opens the document; VC/VI/VA:H on the workstation; SC/SI/SA:H because EHR and clinic systems are subsequently affected. CVSS describes the entry weakness only, not the enterprise impact.</t>
+    <t xml:space="preserve">Representative weakness: malicious macro document leading to code execution (initial vector in E6). AV:L - the document is delivered by e-mail but opened locally on the workstation (FIRST CVSS v4.0 user guide: document-based weaknesses are Local whatever the delivery channel); AC:L; AT:N; PR:N; UI:P user opens the document; VC/VI/VA:H on the workstation; SC/SI/SA:H because EHR and clinic systems are subsequently affected. CVSS describes the entry weakness only, not the enterprise impact.</t>
   </si>
   <si>
     <t xml:space="preserve">MED-CYR-07</t>
@@ -1734,7 +3204,7 @@
     <t xml:space="preserve">Cybercriminal / state-linked actor using public exploits.</t>
   </si>
   <si>
-    <t xml:space="preserve">Patch SLAs and exception governance not evidenced (E7); Incomplete asset inventory (E4); Possible end-of-life systems (Evidence gap)</t>
+    <t xml:space="preserve">Patch SLAs and exception governance not evidenced (E7); Incomplete asset inventory (E4); Possible end-of-life systems (Information gap)</t>
   </si>
   <si>
     <t xml:space="preserve">Firewalls, IDS/IPS (E2); Antimalware (E2)</t>
@@ -1803,7 +3273,7 @@
     <t xml:space="preserve">I01, I03, I11, I12</t>
   </si>
   <si>
-    <t xml:space="preserve">Limited applicability: a detection gap is a control weakness, not a vulnerability. Representative weakness for the workbook: the undetected initial code-execution vector (macro/PowerShell, E6). Do not interpret the score as the severity of the detection gap.</t>
+    <t xml:space="preserve">Limited applicability: a detection gap is a control weakness, not a vulnerability. Representative weakness for the workbook: the undetected initial code-execution vector (macro/PowerShell, E6); AV:L because the malicious document is opened locally. Do not interpret the score as the severity of the detection gap.</t>
   </si>
   <si>
     <t xml:space="preserve">MED-CYR-14</t>
@@ -2760,7 +4230,7 @@
     <t xml:space="preserve">Methodology</t>
   </si>
   <si>
-    <t xml:space="preserve">Authoritative KRI formulas; CVSS v4.0; multiplication factor 1,000 in worked example; reductions must stay within 0-1.</t>
+    <t xml:space="preserve">Authoritative risk-index formulas; CVSS v4.0; multiplication factor 1,000 in worked example; reductions must stay within 0-1.</t>
   </si>
   <si>
     <t xml:space="preserve">E11</t>
@@ -4333,7 +5803,7 @@
       </c>
       <c r="E6" s="7" t="n">
         <f aca="false">Inputs!J5</f>
-        <v>9.4</v>
+        <v>9.3</v>
       </c>
       <c r="F6" s="6" t="n">
         <f aca="false">Inputs!E5</f>
@@ -4361,11 +5831,11 @@
       </c>
       <c r="L6" s="9" t="n">
         <f aca="false">C6*D6*E6*((F6+G6)/2)*H6/I6*K6</f>
-        <v>7893.48214285714</v>
+        <v>7809.50892857143</v>
       </c>
       <c r="M6" s="9" t="n">
         <f aca="false">C6*D6*E6*J6*H6/I6*K6</f>
-        <v>2870.35714285714</v>
+        <v>2839.82142857143</v>
       </c>
       <c r="N6" s="10" t="n">
         <f aca="false">L6/M6</f>
@@ -4385,11 +5855,11 @@
       </c>
       <c r="R6" s="9" t="n">
         <f aca="false">L6*P6*Q6</f>
-        <v>4440.08370535714</v>
+        <v>4392.84877232143</v>
       </c>
       <c r="S6" s="9" t="n">
         <f aca="false">L6-R6</f>
-        <v>3453.3984375</v>
+        <v>3416.66015625</v>
       </c>
       <c r="T6" s="10" t="n">
         <f aca="false">S6/M6</f>
@@ -4401,7 +5871,7 @@
       </c>
       <c r="V6" s="10" t="n">
         <f aca="false">IF(O6=0,0,(L6-S6)/O6*1000)</f>
-        <v>7.57837158130368</v>
+        <v>7.49775060703449</v>
       </c>
       <c r="W6" s="12" t="str">
         <f aca="false">IF(AND(P6&gt;=0,P6&lt;=1,Q6&gt;=0,Q6&lt;=1),"OK","CHECK")</f>
@@ -4897,7 +6367,7 @@
       </c>
       <c r="E12" s="7" t="n">
         <f aca="false">Inputs!J11</f>
-        <v>9.3</v>
+        <v>9.2</v>
       </c>
       <c r="F12" s="6" t="n">
         <f aca="false">Inputs!E11</f>
@@ -4925,11 +6395,11 @@
       </c>
       <c r="L12" s="9" t="n">
         <f aca="false">C12*D12*E12*((F12+G12)/2)*H12/I12*K12</f>
-        <v>9486</v>
+        <v>9384</v>
       </c>
       <c r="M12" s="9" t="n">
         <f aca="false">C12*D12*E12*J12*H12/I12*K12</f>
-        <v>3794.4</v>
+        <v>3753.6</v>
       </c>
       <c r="N12" s="10" t="n">
         <f aca="false">L12/M12</f>
@@ -4949,11 +6419,11 @@
       </c>
       <c r="R12" s="9" t="n">
         <f aca="false">L12*P12*Q12</f>
-        <v>5312.16</v>
+        <v>5255.04</v>
       </c>
       <c r="S12" s="9" t="n">
         <f aca="false">L12-R12</f>
-        <v>4173.84</v>
+        <v>4128.96</v>
       </c>
       <c r="T12" s="10" t="n">
         <f aca="false">S12/M12</f>
@@ -4965,7 +6435,7 @@
       </c>
       <c r="V12" s="10" t="n">
         <f aca="false">IF(O12=0,0,(L12-S12)/O12*1000)</f>
-        <v>25.4305531914894</v>
+        <v>25.1571063829787</v>
       </c>
       <c r="W12" s="12" t="str">
         <f aca="false">IF(AND(P12&gt;=0,P12&lt;=1,Q12&gt;=0,Q12&lt;=1),"OK","CHECK")</f>
@@ -5166,11 +6636,11 @@
       </c>
       <c r="L15" s="14" t="n">
         <f aca="false">SUM(L5:L14)</f>
-        <v>50492.1348214286</v>
+        <v>50306.1616071429</v>
       </c>
       <c r="M15" s="14" t="n">
         <f aca="false">SUM(M5:M14)</f>
-        <v>20507.8888392857</v>
+        <v>20436.553125</v>
       </c>
       <c r="O15" s="15" t="n">
         <f aca="false">SUM(O5:O14)</f>
@@ -5178,19 +6648,19 @@
       </c>
       <c r="R15" s="14" t="n">
         <f aca="false">SUM(R5:R14)</f>
-        <v>27688.1059754464</v>
+        <v>27583.7510424107</v>
       </c>
       <c r="S15" s="14" t="n">
         <f aca="false">SUM(S5:S14)</f>
-        <v>22804.0288459821</v>
+        <v>22722.4105647321</v>
       </c>
       <c r="T15" s="16" t="n">
         <f aca="false">S15/M15</f>
-        <v>1.11196374354721</v>
+        <v>1.11185141769019</v>
       </c>
       <c r="V15" s="16" t="n">
         <f aca="false">(L15-S15)/O15*1000</f>
-        <v>7.16195188190544</v>
+        <v>7.13495888318953</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5516,7 +6986,7 @@
         <v>81</v>
       </c>
       <c r="J5" s="21" t="n">
-        <v>9.4</v>
+        <v>9.3</v>
       </c>
       <c r="K5" s="20" t="n">
         <v>0.75</v>
@@ -5852,7 +7322,7 @@
         <v>99</v>
       </c>
       <c r="J11" s="21" t="n">
-        <v>9.3</v>
+        <v>9.2</v>
       </c>
       <c r="K11" s="20" t="n">
         <v>0.7</v>
@@ -7267,7 +8737,7 @@
       </c>
       <c r="J5" s="7" t="n">
         <f aca="false">Inputs!J5</f>
-        <v>9.4</v>
+        <v>9.3</v>
       </c>
       <c r="K5" s="10" t="n">
         <f aca="false">MAX(0.05,MIN(0.99,Inputs!K5-C5))</f>
@@ -7279,15 +8749,15 @@
       </c>
       <c r="M5" s="9" t="n">
         <f aca="false">D5*E5*J5*((F5+G5)/2)*I5/H5*Parameters!$B$5</f>
-        <v>3740.67777777778</v>
+        <v>3700.88333333333</v>
       </c>
       <c r="N5" s="9" t="n">
         <f aca="false">D5*E5*J5*Parameters!$B$4*I5/H5*Parameters!$B$5</f>
-        <v>1547.86666666667</v>
+        <v>1531.4</v>
       </c>
       <c r="O5" s="9" t="n">
         <f aca="false">M5-M5*K5*L5</f>
-        <v>1038.03808333333</v>
+        <v>1026.995125</v>
       </c>
       <c r="P5" s="10" t="n">
         <f aca="false">O5/N5</f>
@@ -7335,7 +8805,7 @@
       </c>
       <c r="J6" s="7" t="n">
         <f aca="false">Inputs!J5</f>
-        <v>9.4</v>
+        <v>9.3</v>
       </c>
       <c r="K6" s="10" t="n">
         <f aca="false">MAX(0.05,MIN(0.99,Inputs!K5-C6))</f>
@@ -7347,15 +8817,15 @@
       </c>
       <c r="M6" s="9" t="n">
         <f aca="false">D6*E6*J6*((F6+G6)/2)*I6/H6*Parameters!$B$5</f>
-        <v>7893.48214285714</v>
+        <v>7809.50892857143</v>
       </c>
       <c r="N6" s="9" t="n">
         <f aca="false">D6*E6*J6*Parameters!$B$4*I6/H6*Parameters!$B$5</f>
-        <v>2870.35714285714</v>
+        <v>2839.82142857143</v>
       </c>
       <c r="O6" s="9" t="n">
         <f aca="false">M6-M6*K6*L6</f>
-        <v>3453.3984375</v>
+        <v>3416.66015625</v>
       </c>
       <c r="P6" s="10" t="n">
         <f aca="false">O6/N6</f>
@@ -7403,7 +8873,7 @@
       </c>
       <c r="J7" s="7" t="n">
         <f aca="false">Inputs!J5</f>
-        <v>9.4</v>
+        <v>9.3</v>
       </c>
       <c r="K7" s="10" t="n">
         <f aca="false">MAX(0.05,MIN(0.99,Inputs!K5-C7))</f>
@@ -7415,15 +8885,15 @@
       </c>
       <c r="M7" s="9" t="n">
         <f aca="false">D7*E7*J7*((F7+G7)/2)*I7/H7*Parameters!$B$5</f>
-        <v>16304.394</v>
+        <v>16130.943</v>
       </c>
       <c r="N7" s="9" t="n">
         <f aca="false">D7*E7*J7*Parameters!$B$4*I7/H7*Parameters!$B$5</f>
-        <v>5465.16</v>
+        <v>5407.02</v>
       </c>
       <c r="O7" s="9" t="n">
         <f aca="false">M7-M7*K7*L7</f>
-        <v>9415.787535</v>
+        <v>9315.6195825</v>
       </c>
       <c r="P7" s="10" t="n">
         <f aca="false">O7/N7</f>
@@ -8083,7 +9553,7 @@
       </c>
       <c r="J17" s="7" t="n">
         <f aca="false">Inputs!J11</f>
-        <v>9.3</v>
+        <v>9.2</v>
       </c>
       <c r="K17" s="10" t="n">
         <f aca="false">MAX(0.05,MIN(0.99,Inputs!K11-C17))</f>
@@ -8095,15 +9565,15 @@
       </c>
       <c r="M17" s="9" t="n">
         <f aca="false">D17*E17*J17*((F17+G17)/2)*I17/H17*Parameters!$B$5</f>
-        <v>4495.96875</v>
+        <v>4447.625</v>
       </c>
       <c r="N17" s="9" t="n">
         <f aca="false">D17*E17*J17*Parameters!$B$4*I17/H17*Parameters!$B$5</f>
-        <v>2075.0625</v>
+        <v>2052.75</v>
       </c>
       <c r="O17" s="9" t="n">
         <f aca="false">M17-M17*K17*L17</f>
-        <v>1258.87125</v>
+        <v>1245.335</v>
       </c>
       <c r="P17" s="10" t="n">
         <f aca="false">O17/N17</f>
@@ -8151,7 +9621,7 @@
       </c>
       <c r="J18" s="7" t="n">
         <f aca="false">Inputs!J11</f>
-        <v>9.3</v>
+        <v>9.2</v>
       </c>
       <c r="K18" s="10" t="n">
         <f aca="false">MAX(0.05,MIN(0.99,Inputs!K11-C18))</f>
@@ -8163,15 +9633,15 @@
       </c>
       <c r="M18" s="9" t="n">
         <f aca="false">D18*E18*J18*((F18+G18)/2)*I18/H18*Parameters!$B$5</f>
-        <v>9486</v>
+        <v>9384</v>
       </c>
       <c r="N18" s="9" t="n">
         <f aca="false">D18*E18*J18*Parameters!$B$4*I18/H18*Parameters!$B$5</f>
-        <v>3794.4</v>
+        <v>3753.6</v>
       </c>
       <c r="O18" s="9" t="n">
         <f aca="false">M18-M18*K18*L18</f>
-        <v>4173.84</v>
+        <v>4128.96</v>
       </c>
       <c r="P18" s="10" t="n">
         <f aca="false">O18/N18</f>
@@ -8219,7 +9689,7 @@
       </c>
       <c r="J19" s="7" t="n">
         <f aca="false">Inputs!J11</f>
-        <v>9.3</v>
+        <v>9.2</v>
       </c>
       <c r="K19" s="10" t="n">
         <f aca="false">MAX(0.05,MIN(0.99,Inputs!K11-C19))</f>
@@ -8231,15 +9701,15 @@
       </c>
       <c r="M19" s="9" t="n">
         <f aca="false">D19*E19*J19*((F19+G19)/2)*I19/H19*Parameters!$B$5</f>
-        <v>21041.13375</v>
+        <v>20814.885</v>
       </c>
       <c r="N19" s="9" t="n">
         <f aca="false">D19*E19*J19*Parameters!$B$4*I19/H19*Parameters!$B$5</f>
-        <v>7470.225</v>
+        <v>7389.9</v>
       </c>
       <c r="O19" s="9" t="n">
         <f aca="false">M19-M19*K19*L19</f>
-        <v>12203.857575</v>
+        <v>12072.6333</v>
       </c>
       <c r="P19" s="10" t="n">
         <f aca="false">O19/N19</f>
@@ -9041,7 +10511,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
         <v>79</v>
       </c>
